--- a/data_extactor/batch_10_fa/trimmed/batch_0082_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0082_fa_trim.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RepairTRAX | نرم‌افزار کنترل فرایند آماری SPC | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار کنترل فرایند آماری SPC | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word | نرم‌افزار کنترل فرآیند آماری SPC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | چابکی انگشتان | ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | تمایز رنگ‌ها</t>
+          <t>بینایی نزدیک | تجسم | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های لابراتوار چشم‌پزشکی و عینک‌سازی | کارگران فرایندهای عکاسی و اپراتورهای ماشین‌های چاپ و ظهور عکس</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | یادگیری فعال | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | چابکی انگشتان | استدلال قیاسی | درک کتبی | ثبات دست و بازو | چابکی دستی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | مهارت انگشتان | استدلال قیاسی | درک کتبی | ثبات دست و بازو | مهارت دستی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان زیستی و مهندسان پزشکی | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌های ساخت ارتز و پروتز و تجهیزات ارتوپدی | آماده‌سازان و تکنسین‌های استریلیزاسیون تجهیزات پزشکی</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | هنرهای تجسمی و نمایشی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | هنرهای زیبا | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | توجه شنوایی</t>
+          <t>حساسیت شنوایی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | توجه شنیداری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | پرداخت‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | ورق‌کاران و حلبی‌سازان | تعمیرکاران ساعت‌های مچی و دیواری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری و صنایع چوب، به جز اره‌کشی</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران ورق‌کاری فلزی | تعمیرکاران ساعت‌های مچی و دیواری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مکانیک | امور دفتری و اداری | مهندسی و فناوری | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | مکانیک | اداری | مهندسی و فناوری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | ثبات دست و بازو | دقت کنترل | دید نزدیک | چابکی دستی | مرتب‌سازی اطلاعات | تجسم فضایی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | ترتیب‌دهی اطلاعات | تجسم</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | پرداخت‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | فیزیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | فیزیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران ساعت‌های مچی و دیواری | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران ساعت‌های مچی و دیواری | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | قفل‌سازان و تعمیرکاران گاوصندوق | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | ساختمان و سازه | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | زبان انگلیسی | ساختمان و ساخت‌وساز | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | ثبات دست و بازو | چابکی دستی | دید نزدیک | حساسیت به مسئله | دقت کنترل | تجسم فضایی</t>
+          <t>ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مدیران تاسیسات و ساختمان | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع (HVAC) | کمک‌نصابان و کارگران کمکی نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها، نصابان لوله و اتصالات</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مدیران امور ساختمان و تأسیسات | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | شنیدن فعال | سخن گفتن | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | چابکی انگشتان | دید نزدیک | ثبات دست و بازو | چابکی دستی | تعادل کلی بدن</t>
+          <t>حساسیت به مسئله | درک شفاهی | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مهندسان برق | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه‌ها، پست‌ها و رله‌ها | تکنسین‌های نیروگاه‌های برق‌آبی | اپراتورهای نیروگاه برق | نصابان سیستم‌های فتوولتائیک خورشیدی | مهندسان انرژی بادی</t>
+          <t>تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | تکنسین‌های نیروگاه برقابی | اپراتورهای نیروگاه برق | نصابان سیستم‌های خورشیدی فتوولتائیک | مهندسان انرژی باد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مکانیک | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | دید نزدیک | دقت کنترل | مرتب‌سازی اطلاعات | هماهنگی اندام‌های چندگانه</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | ترتیب‌دهی اطلاعات | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | متصدیان ماشین‌های اداری، به جز رایانه</t>
+          <t>تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | فیزیک | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | فیزیک | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی اندام‌های چندگانه | چابکی دستی | درک عمق</t>
+          <t>درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | مهارت دستی | درک عمق</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای لایروب | مهندسان دریایی و معماران کشتی | لوله‌گذاران | ریگرها و متصدیان بستن و مهار بار (طناب‌بندها) | کارگران فنی سکوهای حفاری نفت و گاز (راستابات) | جوشکاران، برشکاران، لحیم‌کاران سخت و نرم</t>
+          <t>کارگران ساختمانی | اپراتورهای لایروب | مهندسان دریایی و معماران کشتی | لوله‌گذاران خطوط انتقال | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران عمومی سکو و میادین نفت و گاز | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | مدیریت و امور اداری | حقوق و مقررات دولتی | رایانه و الکترونیک</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی انگشتان | تجسم فضایی | دقت کنترل | چابکی دستی | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت انگشتان | تجسم | دقت کنترل | مهارت دستی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | برق‌کاران | نصابان و تعمیرکاران آسانسور و پله‌برقی | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | تعمیرکاران درهای مکانیکی و اتوماتیک | نصابان سیستم‌های اعلام سرقت و حریق</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | برق‌کاران | نصابان و تعمیرکاران آسانسور و پله‌برقی | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | تعمیرکاران درب‌های مکانیکی و اتوماتیک | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
